--- a/Minería de datos y modelización predictiva/Plantilla_Respuestas_Test_MineríaDatos_Online.xlsx
+++ b/Minería de datos y modelización predictiva/Plantilla_Respuestas_Test_MineríaDatos_Online.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\PROYECTOS\Minería de datos y modelización predictiva\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6017BC48-4C5C-496F-8319-BF71C1A6EEBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EDFDD58-E896-4FFB-827E-D1D6568EE1FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{FAE37E03-ECC6-4D6A-AA06-AF34559E6D9B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>Pregunta</t>
   </si>
@@ -144,18 +144,6 @@
   </si>
   <si>
     <t>POpc4</t>
-  </si>
-  <si>
-    <t>c</t>
-  </si>
-  <si>
-    <t>a</t>
-  </si>
-  <si>
-    <t>d</t>
-  </si>
-  <si>
-    <t>b</t>
   </si>
 </sst>
 </file>
@@ -715,273 +703,205 @@
       <c r="D6" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="E6" s="1"/>
     </row>
     <row r="7" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="E7" s="1"/>
     </row>
     <row r="8" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D8" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>38</v>
-      </c>
+      <c r="E8" s="1"/>
     </row>
     <row r="9" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D9" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>39</v>
-      </c>
+      <c r="E9" s="1"/>
     </row>
     <row r="10" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D10" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="E10" s="1"/>
     </row>
     <row r="11" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D11" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="E11" s="1"/>
     </row>
     <row r="12" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D12" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="E12" s="1"/>
     </row>
     <row r="13" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D13" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="E13" s="1"/>
     </row>
     <row r="14" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D14" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>38</v>
-      </c>
+      <c r="E14" s="1"/>
     </row>
     <row r="15" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D15" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="E15" s="1"/>
     </row>
     <row r="16" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D16" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>39</v>
-      </c>
+      <c r="E16" s="1"/>
     </row>
     <row r="17" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D17" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E17" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="E17" s="1"/>
     </row>
     <row r="18" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D18" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E18" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="E18" s="1"/>
     </row>
     <row r="19" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D19" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="E19" s="1"/>
     </row>
     <row r="20" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D20" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E20" s="1" t="s">
-        <v>39</v>
-      </c>
+      <c r="E20" s="1"/>
     </row>
     <row r="21" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E21" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="E21" s="1"/>
     </row>
     <row r="22" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="E22" s="1"/>
     </row>
     <row r="23" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E23" s="1" t="s">
-        <v>38</v>
-      </c>
+      <c r="E23" s="1"/>
     </row>
     <row r="24" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E24" s="1" t="s">
-        <v>39</v>
-      </c>
+      <c r="E24" s="1"/>
     </row>
     <row r="25" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E25" s="1" t="s">
-        <v>38</v>
-      </c>
+      <c r="E25" s="1"/>
     </row>
     <row r="26" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E26" s="1" t="s">
-        <v>39</v>
-      </c>
+      <c r="E26" s="1"/>
     </row>
     <row r="27" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E27" s="1" t="s">
-        <v>39</v>
-      </c>
+      <c r="E27" s="1"/>
     </row>
     <row r="28" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E28" s="1" t="s">
-        <v>39</v>
-      </c>
+      <c r="E28" s="1"/>
     </row>
     <row r="29" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E29" s="1" t="s">
-        <v>39</v>
-      </c>
+      <c r="E29" s="1"/>
     </row>
     <row r="30" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E30" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="E30" s="1"/>
     </row>
     <row r="31" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D31" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E31" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="E31" s="1"/>
     </row>
     <row r="32" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D32" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E32" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="E32" s="1"/>
     </row>
     <row r="33" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D33" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E33" s="1" t="s">
-        <v>39</v>
-      </c>
+      <c r="E33" s="1"/>
     </row>
     <row r="34" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D34" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E34" s="1" t="s">
-        <v>38</v>
-      </c>
+      <c r="E34" s="1"/>
     </row>
     <row r="35" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D35" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E35" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="E35" s="1"/>
     </row>
     <row r="36" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D36" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E36" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="E36" s="1"/>
     </row>
     <row r="37" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D37" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E37" s="1" t="s">
-        <v>39</v>
-      </c>
+      <c r="E37" s="1"/>
     </row>
     <row r="38" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D38" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E38" s="1" t="s">
-        <v>38</v>
-      </c>
+      <c r="E38" s="1"/>
     </row>
     <row r="39" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D39" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E39" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="E39" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
